--- a/DataFrame and Coding/Outputs/regression_table.xlsx
+++ b/DataFrame and Coding/Outputs/regression_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matyasvarga-etele/Desktop/Projects/Matyas-Thesis/DataFrame and Coding/Outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B06A239-00DB-E040-B4EF-7F26EE0F74B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB5F073-6314-6F42-97F4-F6C74BD7E236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,36 +20,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="38">
   <si>
     <t>Variable</t>
   </si>
   <si>
-    <t>(1) Baseline</t>
-  </si>
-  <si>
-    <t>(2) + Investment</t>
-  </si>
-  <si>
-    <t>(3) Full controls</t>
+    <t>(1) Baseline Model</t>
+  </si>
+  <si>
+    <t>(2) Extended Model</t>
   </si>
   <si>
     <t>AI trends</t>
   </si>
   <si>
-    <t>-1.326*</t>
-  </si>
-  <si>
-    <t>-1.507</t>
+    <t>-0.177</t>
   </si>
   <si>
     <t>-0.829</t>
   </si>
   <si>
-    <t>(0.758)</t>
-  </si>
-  <si>
-    <t>(1.010)</t>
+    <t>(0.190)</t>
   </si>
   <si>
     <t>(1.040)</t>
@@ -58,19 +49,13 @@
     <t>HDI</t>
   </si>
   <si>
-    <t>31.192</t>
-  </si>
-  <si>
-    <t>18.510</t>
+    <t>0.049</t>
   </si>
   <si>
     <t>1.942</t>
   </si>
   <si>
-    <t>(20.463)</t>
-  </si>
-  <si>
-    <t>(12.650)</t>
+    <t>(7.678)</t>
   </si>
   <si>
     <t>(8.767)</t>
@@ -79,36 +64,21 @@
     <t>AI trends × HDI</t>
   </si>
   <si>
-    <t>1.742*</t>
-  </si>
-  <si>
-    <t>2.055</t>
-  </si>
-  <si>
     <t>0.968</t>
   </si>
   <si>
-    <t>(0.973)</t>
-  </si>
-  <si>
-    <t>(1.295)</t>
-  </si>
-  <si>
     <t>(1.326)</t>
   </si>
   <si>
     <t>Investment</t>
   </si>
   <si>
-    <t>0.169***</t>
+    <t>0.142***</t>
   </si>
   <si>
     <t>0.140***</t>
   </si>
   <si>
-    <t>(0.030)</t>
-  </si>
-  <si>
     <t>(0.025)</t>
   </si>
   <si>
@@ -124,6 +94,9 @@
     <t>Trade openness</t>
   </si>
   <si>
+    <t>0.048***</t>
+  </si>
+  <si>
     <t>0.046***</t>
   </si>
   <si>
@@ -133,6 +106,9 @@
     <t>Inflation</t>
   </si>
   <si>
+    <t>-0.018***</t>
+  </si>
+  <si>
     <t>-0.017***</t>
   </si>
   <si>
@@ -151,10 +127,7 @@
     <t>R-squared</t>
   </si>
   <si>
-    <t>0.309</t>
-  </si>
-  <si>
-    <t>0.333</t>
+    <t>0.381</t>
   </si>
   <si>
     <t>0.382</t>
@@ -167,7 +140,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,13 +153,6 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -224,13 +190,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -534,16 +497,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="122.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -553,211 +515,184 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="D4" t="s">
+      <c r="C6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C7" t="s">
         <v>15</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>16</v>
       </c>
-      <c r="D5" t="s">
+      <c r="B8" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="C8" t="s">
         <v>18</v>
       </c>
-      <c r="B6" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
         <v>19</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>20</v>
       </c>
-      <c r="D6" t="s">
+      <c r="B10" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
         <v>22</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>23</v>
       </c>
-      <c r="D7" t="s">
+      <c r="B12" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="C12" t="s">
         <v>25</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
         <v>26</v>
       </c>
-      <c r="D8" t="s">
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C9" t="s">
+      <c r="B14" t="s">
         <v>28</v>
       </c>
-      <c r="D9" t="s">
+      <c r="C14" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>30</v>
       </c>
-      <c r="D10" t="s">
+      <c r="B16" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D11" t="s">
+      <c r="C16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="B17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>33</v>
       </c>
-      <c r="D12" t="s">
+      <c r="B18">
+        <v>2611</v>
+      </c>
+      <c r="C18">
+        <v>2611</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D13" t="s">
+      <c r="B19" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="C19" t="s">
         <v>36</v>
       </c>
-      <c r="D14" t="s">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18">
-        <v>3220</v>
-      </c>
-      <c r="C18">
-        <v>2694</v>
-      </c>
-      <c r="D18">
-        <v>2611</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A20:D20"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/DataFrame and Coding/Outputs/regression_table.xlsx
+++ b/DataFrame and Coding/Outputs/regression_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matyasvarga-etele/Desktop/Projects/Matyas-Thesis/DataFrame and Coding/Outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB5F073-6314-6F42-97F4-F6C74BD7E236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CCC2EC8-6B29-E04E-A1F5-A98BC41217FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -190,10 +190,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -688,11 +691,16 @@
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+      <c r="A20" s="2" t="s">
         <v>37</v>
       </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A20:C20"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>